--- a/GHG_Trajectory_Analysis_Study/outputs/tables/Analysis_Trajectory Classification.xlsx
+++ b/GHG_Trajectory_Analysis_Study/outputs/tables/Analysis_Trajectory Classification.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:K209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,11 +478,6 @@
           <t>Trajectory_Type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>SDG13.2_Status</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -522,11 +517,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -566,11 +556,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -610,11 +595,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -654,11 +634,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -698,11 +673,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -742,11 +712,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -786,11 +751,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -830,11 +790,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -874,11 +829,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -918,11 +868,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -962,11 +907,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1006,11 +946,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1050,11 +985,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1094,11 +1024,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1138,11 +1063,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1182,11 +1102,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1226,11 +1141,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1270,11 +1180,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1314,11 +1219,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1358,11 +1258,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1402,11 +1297,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1446,11 +1336,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1490,11 +1375,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1534,11 +1414,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1578,11 +1453,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1622,11 +1492,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1666,11 +1531,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1710,11 +1570,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1754,11 +1609,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1798,11 +1648,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1842,11 +1687,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1886,11 +1726,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1930,11 +1765,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1974,11 +1804,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2018,11 +1843,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2062,11 +1882,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2106,11 +1921,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2150,11 +1960,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2194,11 +1999,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2238,11 +2038,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2282,11 +2077,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2326,11 +2116,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2370,11 +2155,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2414,11 +2194,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2458,11 +2233,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2502,11 +2272,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2546,11 +2311,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2590,11 +2350,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2634,11 +2389,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2678,11 +2428,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2722,11 +2467,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2766,11 +2506,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2810,11 +2545,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2854,11 +2584,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2898,11 +2623,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2942,11 +2662,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2986,11 +2701,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3030,11 +2740,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3074,11 +2779,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3118,11 +2818,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3162,11 +2857,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3206,11 +2896,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3250,11 +2935,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3294,11 +2974,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3338,11 +3013,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3382,11 +3052,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3426,11 +3091,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3470,11 +3130,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3514,11 +3169,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3558,11 +3208,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3602,11 +3247,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3646,11 +3286,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3690,11 +3325,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3734,11 +3364,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3778,11 +3403,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3822,11 +3442,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3866,11 +3481,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3910,11 +3520,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3954,11 +3559,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3998,11 +3598,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4042,11 +3637,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4086,11 +3676,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4130,11 +3715,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4174,11 +3754,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4218,11 +3793,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4262,11 +3832,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4306,11 +3871,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4350,11 +3910,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4394,11 +3949,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4438,11 +3988,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4482,11 +4027,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4526,11 +4066,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4570,11 +4105,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4614,11 +4144,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4658,11 +4183,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4702,11 +4222,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4746,11 +4261,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4790,11 +4300,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4834,11 +4339,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4878,11 +4378,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4922,11 +4417,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4966,11 +4456,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5010,11 +4495,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5054,11 +4534,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5098,11 +4573,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5142,11 +4612,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5186,11 +4651,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5230,11 +4690,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5274,11 +4729,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5318,11 +4768,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5362,11 +4807,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5406,11 +4846,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5450,11 +4885,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5494,11 +4924,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5538,11 +4963,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5582,11 +5002,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5626,11 +5041,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5670,11 +5080,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5714,11 +5119,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5758,11 +5158,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5802,11 +5197,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5846,11 +5236,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5890,11 +5275,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5934,11 +5314,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5978,11 +5353,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6022,11 +5392,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6066,11 +5431,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6110,11 +5470,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6154,11 +5509,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6198,11 +5548,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6242,11 +5587,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6286,11 +5626,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6330,11 +5665,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6374,11 +5704,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6418,11 +5743,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6462,11 +5782,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6506,11 +5821,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6550,11 +5860,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6594,11 +5899,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6638,11 +5938,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6682,11 +5977,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6726,11 +6016,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6770,11 +6055,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6814,11 +6094,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6858,11 +6133,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6902,11 +6172,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6946,11 +6211,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6990,11 +6250,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7034,11 +6289,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7078,11 +6328,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7122,11 +6367,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7166,11 +6406,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7210,11 +6445,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7254,11 +6484,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7298,11 +6523,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7342,11 +6562,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7386,11 +6601,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7430,11 +6640,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7474,11 +6679,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7518,11 +6718,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7562,11 +6757,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7606,11 +6796,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7650,11 +6835,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7694,11 +6874,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7738,11 +6913,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7782,11 +6952,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7826,11 +6991,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7870,11 +7030,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7914,11 +7069,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7958,11 +7108,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8002,11 +7147,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8046,11 +7186,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8090,11 +7225,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8134,11 +7264,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8178,11 +7303,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8222,11 +7342,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8266,11 +7381,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8310,11 +7420,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8354,11 +7459,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8398,11 +7498,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8442,11 +7537,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8486,11 +7576,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8530,11 +7615,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8574,11 +7654,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8618,11 +7693,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8662,11 +7732,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8706,11 +7771,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8750,11 +7810,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8794,11 +7849,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8838,11 +7888,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8882,11 +7927,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8926,11 +7966,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8970,11 +8005,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9014,11 +8044,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9058,11 +8083,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9102,11 +8122,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9146,11 +8161,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9190,11 +8200,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9234,11 +8239,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9278,11 +8278,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9322,11 +8317,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9366,11 +8356,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9410,11 +8395,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9454,11 +8434,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9498,11 +8473,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9542,11 +8512,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9586,11 +8551,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9628,11 +8588,6 @@
       <c r="K209" t="inlineStr">
         <is>
           <t>Stable</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
         </is>
       </c>
     </row>
@@ -9647,7 +8602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9658,35 +8613,30 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>SDG 13.2 Status</t>
+          <t>Threshold (1970–2024)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Threshold (1970–2024)</t>
+          <t>N Countries</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>N Countries</t>
+          <t>Share (%)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Share (%)</t>
+          <t>Mean Change (%)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Mean Change (%)</t>
+          <t>Median Change (%)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>Median Change (%)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>Mean Full CAGR (%/yr)</t>
         </is>
@@ -9700,29 +8650,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>&lt; −10%</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="C2" t="n">
         <v>31</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>14.9</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>-37.5</v>
+      </c>
       <c r="F2" t="n">
-        <v>-37.5</v>
+        <v>-34.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-34.3</v>
-      </c>
-      <c r="H2" t="n">
         <v>-0.955</v>
       </c>
     </row>
@@ -9734,29 +8679,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>−10% to +10%</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="C3" t="n">
         <v>11</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="H3" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -9768,29 +8708,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>+10% to +100%</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="C4" t="n">
         <v>30</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>55.6</v>
+      </c>
       <c r="F4" t="n">
-        <v>55.6</v>
+        <v>56.4</v>
       </c>
       <c r="G4" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="H4" t="n">
         <v>0.801</v>
       </c>
     </row>
@@ -9802,29 +8737,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>&gt; +100%</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="C5" t="n">
         <v>136</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>65.4</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>548.5</v>
+      </c>
       <c r="F5" t="n">
-        <v>548.5</v>
+        <v>330.7</v>
       </c>
       <c r="G5" t="n">
-        <v>330.7</v>
-      </c>
-      <c r="H5" t="n">
         <v>2.948</v>
       </c>
     </row>
@@ -9839,7 +8769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9898,11 +8828,6 @@
           <t>Trajectory_Type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>SDG13.2_Status</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9942,11 +8867,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9986,11 +8906,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10030,11 +8945,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10074,11 +8984,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10118,11 +9023,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10162,11 +9062,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10206,11 +9101,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10250,11 +9140,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10294,11 +9179,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10338,11 +9218,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10382,11 +9257,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10426,11 +9296,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10470,11 +9335,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10514,11 +9374,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10558,11 +9413,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10602,11 +9452,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10646,11 +9491,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10690,11 +9530,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10734,11 +9569,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10778,11 +9608,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10822,11 +9647,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10866,11 +9686,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10910,11 +9725,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10954,11 +9764,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10998,11 +9803,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11042,11 +9842,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11086,11 +9881,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11130,11 +9920,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11174,11 +9959,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11218,11 +9998,6 @@
           <t>Declining</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11260,11 +10035,6 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>Declining</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Aligned</t>
         </is>
       </c>
     </row>
@@ -11279,7 +10049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11338,11 +10108,6 @@
           <t>Trajectory_Type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>SDG13.2_Status</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11382,11 +10147,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11426,11 +10186,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11470,11 +10225,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11514,11 +10264,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11558,11 +10303,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11602,11 +10342,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11646,11 +10381,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11690,11 +10420,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11734,11 +10459,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11778,11 +10498,6 @@
           <t>Stable</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11820,11 +10535,6 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>Stable</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Transitioning</t>
         </is>
       </c>
     </row>
@@ -11839,7 +10549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11898,11 +10608,6 @@
           <t>Trajectory_Type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>SDG13.2_Status</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11942,11 +10647,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11986,11 +10686,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12030,11 +10725,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12074,11 +10764,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12118,11 +10803,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12162,11 +10842,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12206,11 +10881,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12250,11 +10920,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12294,11 +10959,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12338,11 +10998,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12382,11 +11037,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12426,11 +11076,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12470,11 +11115,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12514,11 +11154,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12558,11 +11193,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12602,11 +11232,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12646,11 +11271,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12690,11 +11310,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12734,11 +11349,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12778,11 +11388,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12822,11 +11427,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12866,11 +11466,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12910,11 +11505,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12954,11 +11544,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12998,11 +11583,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13042,11 +11622,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13086,11 +11661,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13130,11 +11700,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13174,11 +11739,6 @@
           <t>Moderately Rising</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13216,11 +11776,6 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>Moderately Rising</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>SDG 13.2-At Risk</t>
         </is>
       </c>
     </row>
@@ -13235,7 +11790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13294,11 +11849,6 @@
           <t>Trajectory_Type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>SDG13.2_Status</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13338,11 +11888,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13382,11 +11927,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13426,11 +11966,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13470,11 +12005,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13514,11 +12044,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13558,11 +12083,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13602,11 +12122,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13646,11 +12161,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13690,11 +12200,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13734,11 +12239,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13778,11 +12278,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13822,11 +12317,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13866,11 +12356,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13910,11 +12395,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13954,11 +12434,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13998,11 +12473,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14042,11 +12512,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14086,11 +12551,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14130,11 +12590,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14174,11 +12629,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14218,11 +12668,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14262,11 +12707,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14306,11 +12746,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14350,11 +12785,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14394,11 +12824,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14438,11 +12863,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14482,11 +12902,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14526,11 +12941,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14570,11 +12980,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14614,11 +13019,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14658,11 +13058,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14702,11 +13097,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -14746,11 +13136,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -14790,11 +13175,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14834,11 +13214,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -14878,11 +13253,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -14922,11 +13292,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14966,11 +13331,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -15010,11 +13370,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -15054,11 +13409,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -15098,11 +13448,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -15142,11 +13487,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15186,11 +13526,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -15230,11 +13565,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -15274,11 +13604,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15318,11 +13643,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -15362,11 +13682,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -15406,11 +13721,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -15450,11 +13760,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15494,11 +13799,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -15538,11 +13838,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15582,11 +13877,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15626,11 +13916,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15670,11 +13955,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -15714,11 +13994,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15758,11 +14033,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -15802,11 +14072,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15846,11 +14111,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -15890,11 +14150,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -15934,11 +14189,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -15978,11 +14228,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -16022,11 +14267,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -16066,11 +14306,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -16110,11 +14345,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -16154,11 +14384,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -16198,11 +14423,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -16242,11 +14462,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -16286,11 +14501,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -16330,11 +14540,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -16374,11 +14579,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -16418,11 +14618,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -16462,11 +14657,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -16506,11 +14696,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -16550,11 +14735,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -16594,11 +14774,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -16638,11 +14813,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -16682,11 +14852,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -16726,11 +14891,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -16770,11 +14930,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -16814,11 +14969,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -16858,11 +15008,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -16902,11 +15047,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -16946,11 +15086,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16990,11 +15125,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -17034,11 +15164,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -17078,11 +15203,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -17122,11 +15242,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -17166,11 +15281,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -17210,11 +15320,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -17254,11 +15359,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -17298,11 +15398,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -17342,11 +15437,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -17386,11 +15476,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -17430,11 +15515,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -17474,11 +15554,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -17518,11 +15593,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -17562,11 +15632,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -17606,11 +15671,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -17650,11 +15710,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -17694,11 +15749,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -17738,11 +15788,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -17782,11 +15827,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -17826,11 +15866,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -17870,11 +15905,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -17914,11 +15944,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -17958,11 +15983,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -18002,11 +16022,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -18046,11 +16061,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -18090,11 +16100,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -18134,11 +16139,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -18178,11 +16178,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -18222,11 +16217,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -18266,11 +16256,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -18310,11 +16295,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -18354,11 +16334,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -18398,11 +16373,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -18442,11 +16412,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -18486,11 +16451,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -18530,11 +16490,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -18574,11 +16529,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -18618,11 +16568,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -18662,11 +16607,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -18706,11 +16646,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -18750,11 +16685,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -18794,11 +16724,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -18838,11 +16763,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -18882,11 +16802,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -18926,11 +16841,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -18970,11 +16880,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -19014,11 +16919,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -19058,11 +16958,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -19102,11 +16997,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -19146,11 +17036,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -19190,11 +17075,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -19234,11 +17114,6 @@
           <t>Rapidly Rising</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -19276,11 +17151,6 @@
       <c r="K137" t="inlineStr">
         <is>
           <t>Rapidly Rising</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>SDG 13.2-Critical</t>
         </is>
       </c>
     </row>
